--- a/Result/profitability/4746.xlsx
+++ b/Result/profitability/4746.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.6812500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>39.87625</v>
+        <v>39.6125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="N3" t="n">
-        <v>37.43125</v>
+        <v>37.135</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9675</v>
+        <v>0.8275</v>
       </c>
       <c r="N4" t="n">
-        <v>35.555</v>
+        <v>35.17875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8862500000000001</v>
+        <v>1.0275</v>
       </c>
       <c r="N5" t="n">
-        <v>32.74625</v>
+        <v>32.42625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2675</v>
+        <v>0.915</v>
       </c>
       <c r="N6" t="n">
-        <v>30.91875</v>
+        <v>30.5025</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>99.2</v>
@@ -1264,10 +1264,10 @@
         <v>1.13</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07125</v>
+        <v>0.9025000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>28.87875</v>
+        <v>28.56</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>99.3</v>
@@ -1391,10 +1391,10 @@
         <v>0.82</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>0.985</v>
       </c>
       <c r="N8" t="n">
-        <v>26.3075</v>
+        <v>25.815</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>99.40000000000001</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1111</v>
+      </c>
+      <c r="D70" t="n">
+        <v>677</v>
+      </c>
+      <c r="E70" t="n">
+        <v>434</v>
+      </c>
+      <c r="F70" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="G70" t="n">
+        <v>86</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>7.75%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>-112</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.4337500000000001</v>
+      </c>
+      <c r="N70" t="n">
+        <v>41.52375</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>-3.939999999999998</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-0.09167054443927403</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-0.904</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-2.560000000000002</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>-0.06153846153846154</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
